--- a/data/fire_brigade/data.xlsx
+++ b/data/fire_brigade/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H96"/>
+  <dimension ref="A1:H95"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1401,7 +1401,7 @@
         <v>高松市消防団前田分団第１部屯所</v>
       </c>
       <c r="E39" t="str">
-        <v>高松市亀田町172-7</v>
+        <v>高松市亀田町195-8</v>
       </c>
       <c r="F39" t="str">
         <v>087-861-2503</v>
@@ -1986,6 +1986,9 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="str">
+        <v/>
+      </c>
       <c r="B62" t="str">
         <v>34.19596225788533</v>
       </c>
@@ -2003,6 +2006,9 @@
       </c>
       <c r="G62" t="str">
         <v>http://www.city.takamatsu.kagawa.jp/kurashi/kurashi/shobo/shobo/shobodan/dai7.html</v>
+      </c>
+      <c r="H62" t="str">
+        <v/>
       </c>
     </row>
     <row r="63">
@@ -2605,19 +2611,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B86" t="str">
-        <v>34.37932</v>
+        <v>34.36845</v>
       </c>
       <c r="C86" t="str">
-        <v>134.12828</v>
+        <v>134.12069</v>
       </c>
       <c r="D86" t="str">
-        <v>高松市消防団庵治分団第４部湯谷屯所</v>
+        <v>高松市消防団庵治分団第４部新開屯所</v>
       </c>
       <c r="E86" t="str">
-        <v>高松市庵治町333-2</v>
+        <v>高松市庵治町6392-59</v>
       </c>
       <c r="F86" t="str">
         <v>087-861-2503</v>
@@ -2631,19 +2637,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B87" t="str">
-        <v>34.36845</v>
+        <v>34.32718</v>
       </c>
       <c r="C87" t="str">
-        <v>134.12069</v>
+        <v>134.15335</v>
       </c>
       <c r="D87" t="str">
-        <v>高松市消防団庵治分団第４部深間屯所</v>
+        <v>高松市消防団牟礼分団第１部屯所</v>
       </c>
       <c r="E87" t="str">
-        <v>高松市庵治町6391-17</v>
+        <v>高松市牟礼町原766</v>
       </c>
       <c r="F87" t="str">
         <v>087-861-2503</v>
@@ -2657,19 +2663,19 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B88" t="str">
-        <v>34.32718</v>
+        <v>34.33599</v>
       </c>
       <c r="C88" t="str">
-        <v>134.15335</v>
+        <v>134.1427</v>
       </c>
       <c r="D88" t="str">
-        <v>高松市消防団牟礼分団第１部屯所</v>
+        <v>高松市消防団牟礼分団第２部屯所</v>
       </c>
       <c r="E88" t="str">
-        <v>高松市牟礼町原766</v>
+        <v>高松市牟礼町大町1459-2</v>
       </c>
       <c r="F88" t="str">
         <v>087-861-2503</v>
@@ -2683,19 +2689,19 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B89" t="str">
-        <v>34.33599</v>
+        <v>34.35002</v>
       </c>
       <c r="C89" t="str">
-        <v>134.1427</v>
+        <v>134.12692</v>
       </c>
       <c r="D89" t="str">
-        <v>高松市消防団牟礼分団第２部屯所</v>
+        <v>高松市消防団牟礼分団第３部屯所</v>
       </c>
       <c r="E89" t="str">
-        <v>高松市牟礼町大町1459-2</v>
+        <v>高松市牟礼町牟礼3029-1</v>
       </c>
       <c r="F89" t="str">
         <v>087-861-2503</v>
@@ -2709,19 +2715,19 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B90" t="str">
-        <v>34.35002</v>
+        <v>34.34061</v>
       </c>
       <c r="C90" t="str">
-        <v>134.12692</v>
+        <v>134.13399</v>
       </c>
       <c r="D90" t="str">
-        <v>高松市消防団牟礼分団第３部屯所</v>
+        <v>高松市消防団牟礼分団第４部屯所</v>
       </c>
       <c r="E90" t="str">
-        <v>高松市牟礼町牟礼3029-1</v>
+        <v>高松市牟礼町牟礼1118-1</v>
       </c>
       <c r="F90" t="str">
         <v>087-861-2503</v>
@@ -2735,25 +2741,25 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B91" t="str">
-        <v>34.34061</v>
+        <v>34.31271</v>
       </c>
       <c r="C91" t="str">
-        <v>134.13399</v>
+        <v>134.0662</v>
       </c>
       <c r="D91" t="str">
-        <v>高松市消防団牟礼分団第４部屯所</v>
+        <v>高松市消防団木太分団第３部屯所</v>
       </c>
       <c r="E91" t="str">
-        <v>高松市牟礼町牟礼1118-1</v>
+        <v>高松市木太町5096-1</v>
       </c>
       <c r="F91" t="str">
         <v>087-861-2503</v>
       </c>
       <c r="G91" t="str">
-        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kurashi/shobo/shobo/shobodan/dai8.html</v>
+        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kurashi/shobo/shobo/shobodan/dai4.html</v>
       </c>
       <c r="H91" t="str">
         <v/>
@@ -2761,25 +2767,25 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B92" t="str">
-        <v>34.31271</v>
+        <v>34.3901</v>
       </c>
       <c r="C92" t="str">
-        <v>134.0662</v>
+        <v>134.05301</v>
       </c>
       <c r="D92" t="str">
-        <v>高松市消防団木太分団第３部屯所</v>
+        <v>高松市消防団女木分団東浦消防屯所車庫</v>
       </c>
       <c r="E92" t="str">
-        <v>高松市木太町5096-1</v>
+        <v>高松市女木町235-1</v>
       </c>
       <c r="F92" t="str">
         <v>087-861-2503</v>
       </c>
       <c r="G92" t="str">
-        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kurashi/shobo/shobo/shobodan/dai4.html</v>
+        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kurashi/shobo/shobo/shobodan/dai1.html</v>
       </c>
       <c r="H92" t="str">
         <v/>
@@ -2787,19 +2793,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B93" t="str">
-        <v>34.3901</v>
+        <v>34.39484</v>
       </c>
       <c r="C93" t="str">
-        <v>134.05301</v>
+        <v>134.04418</v>
       </c>
       <c r="D93" t="str">
-        <v>高松市消防団女木分団東浦消防屯所車庫</v>
+        <v>高松市消防団女木分団西浦消防屯所車庫</v>
       </c>
       <c r="E93" t="str">
-        <v>高松市女木町235-1</v>
+        <v>高松市女木町2943</v>
       </c>
       <c r="F93" t="str">
         <v>087-861-2503</v>
@@ -2813,19 +2819,19 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>96</v>
+        <v/>
       </c>
       <c r="B94" t="str">
-        <v>34.39484</v>
+        <v>34.39506251264558</v>
       </c>
       <c r="C94" t="str">
-        <v>134.04418</v>
+        <v>134.04450044702173</v>
       </c>
       <c r="D94" t="str">
-        <v>高松市消防団女木分団西浦消防屯所車庫</v>
+        <v>高松市消防団女木分団西浦消防屯所倉庫</v>
       </c>
       <c r="E94" t="str">
-        <v>高松市女木町2943</v>
+        <v>高松市女木町西浦1906地先</v>
       </c>
       <c r="F94" t="str">
         <v>087-861-2503</v>
@@ -2838,54 +2844,34 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="str">
+        <v>72</v>
+      </c>
       <c r="B95" t="str">
-        <v>34.39506251264558</v>
+        <v>34.24382</v>
       </c>
       <c r="C95" t="str">
-        <v>134.04450044702173</v>
+        <v>134.027</v>
       </c>
       <c r="D95" t="str">
-        <v>高松市消防団女木分団西浦消防屯所倉庫</v>
+        <v>高松市消防団香川分団第３部川東下屯所</v>
       </c>
       <c r="E95" t="str">
-        <v>高松市女木町西浦1906地先</v>
+        <v>高松市香川町川東下765-7</v>
       </c>
       <c r="F95" t="str">
         <v>087-861-2503</v>
       </c>
       <c r="G95" t="str">
-        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kurashi/shobo/shobo/shobodan/dai1.html</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>72</v>
-      </c>
-      <c r="B96" t="str">
-        <v>34.24382</v>
-      </c>
-      <c r="C96" t="str">
-        <v>134.027</v>
-      </c>
-      <c r="D96" t="str">
-        <v>高松市消防団香川分団第３部川東下屯所</v>
-      </c>
-      <c r="E96" t="str">
-        <v>高松市香川町川東下765-7</v>
-      </c>
-      <c r="F96" t="str">
-        <v>087-861-2503</v>
-      </c>
-      <c r="G96" t="str">
         <v>http://www.city.takamatsu.kagawa.jp/kurashi/kurashi/shobo/shobo/shobodan/dai7.html</v>
       </c>
-      <c r="H96" t="str">
+      <c r="H95" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H96"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H95"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/fire_brigade/data.xlsx
+++ b/data/fire_brigade/data.xlsx
@@ -1392,10 +1392,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>34.28469</v>
+        <v>34.28538</v>
       </c>
       <c r="C39" t="str">
-        <v>134.11363</v>
+        <v>134.1135</v>
       </c>
       <c r="D39" t="str">
         <v>高松市消防団前田分団第１部屯所</v>
@@ -2614,10 +2614,10 @@
         <v>89</v>
       </c>
       <c r="B86" t="str">
-        <v>34.36845</v>
+        <v>34.38089</v>
       </c>
       <c r="C86" t="str">
-        <v>134.12069</v>
+        <v>134.12673</v>
       </c>
       <c r="D86" t="str">
         <v>高松市消防団庵治分団第４部新開屯所</v>

--- a/data/fire_brigade/data.xlsx
+++ b/data/fire_brigade/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H95"/>
+  <dimension ref="A1:H94"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2429,19 +2429,19 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B79" t="str">
-        <v>34.39184</v>
+        <v>34.39863</v>
       </c>
       <c r="C79" t="str">
-        <v>134.1263</v>
+        <v>134.13673</v>
       </c>
       <c r="D79" t="str">
-        <v>高松市消防団庵治分団第２部王の下屯所</v>
+        <v>高松市消防団庵治分団第２部竹居屯所</v>
       </c>
       <c r="E79" t="str">
-        <v>高松市庵治町6368-28</v>
+        <v>高松市庵治町5385-4</v>
       </c>
       <c r="F79" t="str">
         <v>087-861-2503</v>
@@ -2455,19 +2455,19 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B80" t="str">
-        <v>34.39863</v>
+        <v>34.39163</v>
       </c>
       <c r="C80" t="str">
-        <v>134.13673</v>
+        <v>134.15257</v>
       </c>
       <c r="D80" t="str">
-        <v>高松市消防団庵治分団第２部竹居屯所</v>
+        <v>高松市消防団庵治分団第２部鎌野屯所</v>
       </c>
       <c r="E80" t="str">
-        <v>高松市庵治町5385-4</v>
+        <v>高松市庵治町4511-20</v>
       </c>
       <c r="F80" t="str">
         <v>087-861-2503</v>
@@ -2481,19 +2481,19 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B81" t="str">
-        <v>34.39163</v>
+        <v>34.38681</v>
       </c>
       <c r="C81" t="str">
-        <v>134.15257</v>
+        <v>134.13488</v>
       </c>
       <c r="D81" t="str">
-        <v>高松市消防団庵治分団第２部鎌野屯所</v>
+        <v>高松市消防団庵治分団第３部北村屯所</v>
       </c>
       <c r="E81" t="str">
-        <v>高松市庵治町4511-20</v>
+        <v>高松市庵治町1088</v>
       </c>
       <c r="F81" t="str">
         <v>087-861-2503</v>
@@ -2507,19 +2507,19 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B82" t="str">
-        <v>34.38681</v>
+        <v>34.38057</v>
       </c>
       <c r="C82" t="str">
-        <v>134.13488</v>
+        <v>134.14153</v>
       </c>
       <c r="D82" t="str">
-        <v>高松市消防団庵治分団第３部北村屯所</v>
+        <v>高松市消防団庵治分団第３部宮東屯所</v>
       </c>
       <c r="E82" t="str">
-        <v>高松市庵治町1088</v>
+        <v>高松市庵治町4083</v>
       </c>
       <c r="F82" t="str">
         <v>087-861-2503</v>
@@ -2533,19 +2533,19 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B83" t="str">
-        <v>34.38057</v>
+        <v>34.3753</v>
       </c>
       <c r="C83" t="str">
-        <v>134.14153</v>
+        <v>134.13801</v>
       </c>
       <c r="D83" t="str">
-        <v>高松市消防団庵治分団第３部宮東屯所</v>
+        <v>高松市消防団庵治分団第３部松尾屯所</v>
       </c>
       <c r="E83" t="str">
-        <v>高松市庵治町4083</v>
+        <v>高松市庵治町2290-1</v>
       </c>
       <c r="F83" t="str">
         <v>087-861-2503</v>
@@ -2559,19 +2559,19 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" t="str">
-        <v>34.3753</v>
+        <v>34.36307</v>
       </c>
       <c r="C84" t="str">
-        <v>134.13801</v>
+        <v>134.15707</v>
       </c>
       <c r="D84" t="str">
-        <v>高松市消防団庵治分団第３部松尾屯所</v>
+        <v>高松市消防団庵治分団第４部高尻屯所</v>
       </c>
       <c r="E84" t="str">
-        <v>高松市庵治町2290-1</v>
+        <v>高松市庵治町2914</v>
       </c>
       <c r="F84" t="str">
         <v>087-861-2503</v>
@@ -2585,19 +2585,19 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B85" t="str">
-        <v>34.36307</v>
+        <v>34.38089</v>
       </c>
       <c r="C85" t="str">
-        <v>134.15707</v>
+        <v>134.12673</v>
       </c>
       <c r="D85" t="str">
-        <v>高松市消防団庵治分団第４部高尻屯所</v>
+        <v>高松市消防団庵治分団第４部新開屯所</v>
       </c>
       <c r="E85" t="str">
-        <v>高松市庵治町2914</v>
+        <v>高松市庵治町6392-59</v>
       </c>
       <c r="F85" t="str">
         <v>087-861-2503</v>
@@ -2611,19 +2611,19 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B86" t="str">
-        <v>34.38089</v>
+        <v>34.32718</v>
       </c>
       <c r="C86" t="str">
-        <v>134.12673</v>
+        <v>134.15335</v>
       </c>
       <c r="D86" t="str">
-        <v>高松市消防団庵治分団第４部新開屯所</v>
+        <v>高松市消防団牟礼分団第１部屯所</v>
       </c>
       <c r="E86" t="str">
-        <v>高松市庵治町6392-59</v>
+        <v>高松市牟礼町原766</v>
       </c>
       <c r="F86" t="str">
         <v>087-861-2503</v>
@@ -2637,19 +2637,19 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B87" t="str">
-        <v>34.32718</v>
+        <v>34.33599</v>
       </c>
       <c r="C87" t="str">
-        <v>134.15335</v>
+        <v>134.1427</v>
       </c>
       <c r="D87" t="str">
-        <v>高松市消防団牟礼分団第１部屯所</v>
+        <v>高松市消防団牟礼分団第２部屯所</v>
       </c>
       <c r="E87" t="str">
-        <v>高松市牟礼町原766</v>
+        <v>高松市牟礼町大町1459-2</v>
       </c>
       <c r="F87" t="str">
         <v>087-861-2503</v>
@@ -2663,19 +2663,19 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B88" t="str">
-        <v>34.33599</v>
+        <v>34.35002</v>
       </c>
       <c r="C88" t="str">
-        <v>134.1427</v>
+        <v>134.12692</v>
       </c>
       <c r="D88" t="str">
-        <v>高松市消防団牟礼分団第２部屯所</v>
+        <v>高松市消防団牟礼分団第３部屯所</v>
       </c>
       <c r="E88" t="str">
-        <v>高松市牟礼町大町1459-2</v>
+        <v>高松市牟礼町牟礼3029-1</v>
       </c>
       <c r="F88" t="str">
         <v>087-861-2503</v>
@@ -2689,19 +2689,19 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B89" t="str">
-        <v>34.35002</v>
+        <v>34.34061</v>
       </c>
       <c r="C89" t="str">
-        <v>134.12692</v>
+        <v>134.13399</v>
       </c>
       <c r="D89" t="str">
-        <v>高松市消防団牟礼分団第３部屯所</v>
+        <v>高松市消防団牟礼分団第４部屯所</v>
       </c>
       <c r="E89" t="str">
-        <v>高松市牟礼町牟礼3029-1</v>
+        <v>高松市牟礼町牟礼1118-1</v>
       </c>
       <c r="F89" t="str">
         <v>087-861-2503</v>
@@ -2715,25 +2715,25 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B90" t="str">
-        <v>34.34061</v>
+        <v>34.31271</v>
       </c>
       <c r="C90" t="str">
-        <v>134.13399</v>
+        <v>134.0662</v>
       </c>
       <c r="D90" t="str">
-        <v>高松市消防団牟礼分団第４部屯所</v>
+        <v>高松市消防団木太分団第３部屯所</v>
       </c>
       <c r="E90" t="str">
-        <v>高松市牟礼町牟礼1118-1</v>
+        <v>高松市木太町5096-1</v>
       </c>
       <c r="F90" t="str">
         <v>087-861-2503</v>
       </c>
       <c r="G90" t="str">
-        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kurashi/shobo/shobo/shobodan/dai8.html</v>
+        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kurashi/shobo/shobo/shobodan/dai4.html</v>
       </c>
       <c r="H90" t="str">
         <v/>
@@ -2741,25 +2741,25 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B91" t="str">
-        <v>34.31271</v>
+        <v>34.3901</v>
       </c>
       <c r="C91" t="str">
-        <v>134.0662</v>
+        <v>134.05301</v>
       </c>
       <c r="D91" t="str">
-        <v>高松市消防団木太分団第３部屯所</v>
+        <v>高松市消防団女木分団東浦消防屯所車庫</v>
       </c>
       <c r="E91" t="str">
-        <v>高松市木太町5096-1</v>
+        <v>高松市女木町235-1</v>
       </c>
       <c r="F91" t="str">
         <v>087-861-2503</v>
       </c>
       <c r="G91" t="str">
-        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kurashi/shobo/shobo/shobodan/dai4.html</v>
+        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kurashi/shobo/shobo/shobodan/dai1.html</v>
       </c>
       <c r="H91" t="str">
         <v/>
@@ -2767,19 +2767,19 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B92" t="str">
-        <v>34.3901</v>
+        <v>34.39484</v>
       </c>
       <c r="C92" t="str">
-        <v>134.05301</v>
+        <v>134.04418</v>
       </c>
       <c r="D92" t="str">
-        <v>高松市消防団女木分団東浦消防屯所車庫</v>
+        <v>高松市消防団女木分団西浦消防屯所車庫</v>
       </c>
       <c r="E92" t="str">
-        <v>高松市女木町235-1</v>
+        <v>高松市女木町2943</v>
       </c>
       <c r="F92" t="str">
         <v>087-861-2503</v>
@@ -2793,19 +2793,19 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>96</v>
+        <v/>
       </c>
       <c r="B93" t="str">
-        <v>34.39484</v>
+        <v>34.39506251264558</v>
       </c>
       <c r="C93" t="str">
-        <v>134.04418</v>
+        <v>134.04450044702173</v>
       </c>
       <c r="D93" t="str">
-        <v>高松市消防団女木分団西浦消防屯所車庫</v>
+        <v>高松市消防団女木分団西浦消防屯所倉庫</v>
       </c>
       <c r="E93" t="str">
-        <v>高松市女木町2943</v>
+        <v>高松市女木町西浦1906地先</v>
       </c>
       <c r="F93" t="str">
         <v>087-861-2503</v>
@@ -2819,59 +2819,33 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v/>
+        <v>72</v>
       </c>
       <c r="B94" t="str">
-        <v>34.39506251264558</v>
+        <v>34.24382</v>
       </c>
       <c r="C94" t="str">
-        <v>134.04450044702173</v>
+        <v>134.027</v>
       </c>
       <c r="D94" t="str">
-        <v>高松市消防団女木分団西浦消防屯所倉庫</v>
+        <v>高松市消防団香川分団第３部川東下屯所</v>
       </c>
       <c r="E94" t="str">
-        <v>高松市女木町西浦1906地先</v>
+        <v>高松市香川町川東下765-7</v>
       </c>
       <c r="F94" t="str">
         <v>087-861-2503</v>
       </c>
       <c r="G94" t="str">
-        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kurashi/shobo/shobo/shobodan/dai1.html</v>
+        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kurashi/shobo/shobo/shobodan/dai7.html</v>
       </c>
       <c r="H94" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>72</v>
-      </c>
-      <c r="B95" t="str">
-        <v>34.24382</v>
-      </c>
-      <c r="C95" t="str">
-        <v>134.027</v>
-      </c>
-      <c r="D95" t="str">
-        <v>高松市消防団香川分団第３部川東下屯所</v>
-      </c>
-      <c r="E95" t="str">
-        <v>高松市香川町川東下765-7</v>
-      </c>
-      <c r="F95" t="str">
-        <v>087-861-2503</v>
-      </c>
-      <c r="G95" t="str">
-        <v>http://www.city.takamatsu.kagawa.jp/kurashi/kurashi/shobo/shobo/shobodan/dai7.html</v>
-      </c>
-      <c r="H95" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H95"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H94"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/fire_brigade/data.xlsx
+++ b/data/fire_brigade/data.xlsx
@@ -1002,10 +1002,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>34.30099</v>
+        <v>34.2974</v>
       </c>
       <c r="C24" t="str">
-        <v>134.0319</v>
+        <v>134.0270</v>
       </c>
       <c r="D24" t="str">
         <v>高松市消防団一宮分団第２部屯所</v>
